--- a/research/traditional_assets/database/data/denmark/denmark_coal_related_energy.xlsx
+++ b/research/traditional_assets/database/data/denmark/denmark_coal_related_energy.xlsx
@@ -588,22 +588,22 @@
         </is>
       </c>
       <c r="G2">
-        <v>-5.833333333333333</v>
+        <v>-9.411057692307693</v>
       </c>
       <c r="H2">
-        <v>-5.833333333333333</v>
+        <v>-9.579326923076923</v>
       </c>
       <c r="I2">
-        <v>-19.59770114942529</v>
+        <v>-15.98557692307693</v>
       </c>
       <c r="J2">
-        <v>-19.59770114942529</v>
+        <v>-15.98557692307693</v>
       </c>
       <c r="K2">
-        <v>-3.95</v>
+        <v>-14.7</v>
       </c>
       <c r="L2">
-        <v>-11.35057471264368</v>
+        <v>-17.66826923076923</v>
       </c>
       <c r="M2">
         <v>0</v>
@@ -627,58 +627,73 @@
         <v>0</v>
       </c>
       <c r="U2">
-        <v>80.5</v>
+        <v>40</v>
       </c>
       <c r="V2">
-        <v>0.2375331956329301</v>
+        <v>0.1403508771929824</v>
+      </c>
+      <c r="W2">
+        <v>-0.1620727673649393</v>
       </c>
       <c r="X2">
-        <v>0.05882040299968754</v>
+        <v>0.1214544444345108</v>
+      </c>
+      <c r="Y2">
+        <v>-0.2835272117994502</v>
+      </c>
+      <c r="Z2">
+        <v>0.07648464791321934</v>
+      </c>
+      <c r="AA2">
+        <v>-1.222651222651223</v>
       </c>
       <c r="AB2">
-        <v>0.05884758451925968</v>
+        <v>0.1186453400805256</v>
+      </c>
+      <c r="AC2">
+        <v>-1.341296562731748</v>
       </c>
       <c r="AD2">
-        <v>0.678</v>
+        <v>11</v>
       </c>
       <c r="AE2">
         <v>0</v>
       </c>
       <c r="AF2">
-        <v>0.678</v>
+        <v>11</v>
       </c>
       <c r="AG2">
-        <v>-79.822</v>
+        <v>-29</v>
       </c>
       <c r="AH2">
-        <v>0.001996595774755726</v>
+        <v>0.03716216216216216</v>
       </c>
       <c r="AI2">
-        <v>0.007222139372376916</v>
+        <v>0.1453104359313078</v>
       </c>
       <c r="AJ2">
-        <v>-0.3081002632411861</v>
+        <v>-0.11328125</v>
       </c>
       <c r="AK2">
-        <v>-5.966661683360742</v>
+        <v>-0.8123249299719887</v>
       </c>
       <c r="AL2">
-        <v>0.464</v>
+        <v>2.75</v>
       </c>
       <c r="AM2">
-        <v>-1.266</v>
+        <v>2.75</v>
       </c>
       <c r="AN2">
-        <v>-0.1086538461538462</v>
+        <v>-0.990990990990991</v>
       </c>
       <c r="AO2">
-        <v>-14.69827586206897</v>
+        <v>-4.836363636363637</v>
       </c>
       <c r="AP2">
-        <v>12.79198717948718</v>
+        <v>2.612612612612613</v>
       </c>
       <c r="AQ2">
-        <v>5.387045813586098</v>
+        <v>-4.836363636363637</v>
       </c>
     </row>
     <row r="3">
@@ -698,22 +713,22 @@
         </is>
       </c>
       <c r="G3">
-        <v>-5.833333333333333</v>
+        <v>-9.411057692307693</v>
       </c>
       <c r="H3">
-        <v>-5.833333333333333</v>
+        <v>-9.579326923076923</v>
       </c>
       <c r="I3">
-        <v>-19.59770114942529</v>
+        <v>-15.98557692307693</v>
       </c>
       <c r="J3">
-        <v>-19.59770114942529</v>
+        <v>-15.98557692307693</v>
       </c>
       <c r="K3">
-        <v>-3.95</v>
+        <v>-14.7</v>
       </c>
       <c r="L3">
-        <v>-11.35057471264368</v>
+        <v>-17.66826923076923</v>
       </c>
       <c r="M3">
         <v>-0</v>
@@ -737,58 +752,73 @@
         <v>0</v>
       </c>
       <c r="U3">
-        <v>80.5</v>
+        <v>40</v>
       </c>
       <c r="V3">
-        <v>0.2375331956329301</v>
+        <v>0.1403508771929824</v>
+      </c>
+      <c r="W3">
+        <v>-0.1620727673649393</v>
       </c>
       <c r="X3">
-        <v>0.05882040299968754</v>
+        <v>0.1214544444345108</v>
+      </c>
+      <c r="Y3">
+        <v>-0.2835272117994502</v>
+      </c>
+      <c r="Z3">
+        <v>0.07648464791321934</v>
+      </c>
+      <c r="AA3">
+        <v>-1.222651222651223</v>
       </c>
       <c r="AB3">
-        <v>0.05884758451925968</v>
+        <v>0.1186453400805256</v>
+      </c>
+      <c r="AC3">
+        <v>-1.341296562731748</v>
       </c>
       <c r="AD3">
-        <v>0.678</v>
+        <v>11</v>
       </c>
       <c r="AE3">
         <v>0</v>
       </c>
       <c r="AF3">
-        <v>0.678</v>
+        <v>11</v>
       </c>
       <c r="AG3">
-        <v>-79.822</v>
+        <v>-29</v>
       </c>
       <c r="AH3">
-        <v>0.001996595774755726</v>
+        <v>0.03716216216216216</v>
       </c>
       <c r="AI3">
-        <v>0.007222139372376916</v>
+        <v>0.1453104359313078</v>
       </c>
       <c r="AJ3">
-        <v>-0.3081002632411861</v>
+        <v>-0.11328125</v>
       </c>
       <c r="AK3">
-        <v>-5.966661683360742</v>
+        <v>-0.8123249299719887</v>
       </c>
       <c r="AL3">
-        <v>0.464</v>
+        <v>2.75</v>
       </c>
       <c r="AM3">
-        <v>-1.266</v>
+        <v>2.75</v>
       </c>
       <c r="AN3">
-        <v>-0.1086538461538462</v>
+        <v>-0.990990990990991</v>
       </c>
       <c r="AO3">
-        <v>-14.69827586206897</v>
+        <v>-4.836363636363637</v>
       </c>
       <c r="AP3">
-        <v>12.79198717948718</v>
+        <v>2.612612612612613</v>
       </c>
       <c r="AQ3">
-        <v>5.387045813586098</v>
+        <v>-4.836363636363637</v>
       </c>
     </row>
   </sheetData>

--- a/research/traditional_assets/database/data/denmark/denmark_coal_related_energy.xlsx
+++ b/research/traditional_assets/database/data/denmark/denmark_coal_related_energy.xlsx
@@ -588,22 +588,22 @@
         </is>
       </c>
       <c r="G2">
-        <v>-9.411057692307693</v>
+        <v>-4.482935153583617</v>
       </c>
       <c r="H2">
-        <v>-9.579326923076923</v>
+        <v>-4.573378839590443</v>
       </c>
       <c r="I2">
-        <v>-15.98557692307693</v>
+        <v>-7.918088737201365</v>
       </c>
       <c r="J2">
-        <v>-15.98557692307693</v>
+        <v>-7.918088737201365</v>
       </c>
       <c r="K2">
-        <v>-14.7</v>
+        <v>-23</v>
       </c>
       <c r="L2">
-        <v>-17.66826923076923</v>
+        <v>-7.849829351535836</v>
       </c>
       <c r="M2">
         <v>0</v>
@@ -627,73 +627,73 @@
         <v>0</v>
       </c>
       <c r="U2">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="V2">
-        <v>0.1403508771929824</v>
+        <v>0.5333333333333333</v>
       </c>
       <c r="W2">
-        <v>-0.1620727673649393</v>
+        <v>-0.3662420382165605</v>
       </c>
       <c r="X2">
-        <v>0.1214544444345108</v>
+        <v>0.09937984110353799</v>
       </c>
       <c r="Y2">
-        <v>-0.2835272117994502</v>
+        <v>-0.4656218793200985</v>
       </c>
       <c r="Z2">
-        <v>0.07648464791321934</v>
+        <v>0.08668639053254439</v>
       </c>
       <c r="AA2">
-        <v>-1.222651222651223</v>
+        <v>-0.6863905325443788</v>
       </c>
       <c r="AB2">
-        <v>0.1186453400805256</v>
+        <v>0.08648018135294791</v>
       </c>
       <c r="AC2">
-        <v>-1.341296562731748</v>
+        <v>-0.7728707138973266</v>
       </c>
       <c r="AD2">
-        <v>11</v>
+        <v>18.6</v>
       </c>
       <c r="AE2">
         <v>0</v>
       </c>
       <c r="AF2">
-        <v>11</v>
+        <v>18.6</v>
       </c>
       <c r="AG2">
-        <v>-29</v>
+        <v>-17.4</v>
       </c>
       <c r="AH2">
-        <v>0.03716216216216216</v>
+        <v>0.21602787456446</v>
       </c>
       <c r="AI2">
-        <v>0.1453104359313078</v>
+        <v>0.1790182868142445</v>
       </c>
       <c r="AJ2">
-        <v>-0.11328125</v>
+        <v>-0.3473053892215568</v>
       </c>
       <c r="AK2">
-        <v>-0.8123249299719887</v>
+        <v>-0.2562592047128129</v>
       </c>
       <c r="AL2">
-        <v>2.75</v>
+        <v>0.5669999999999999</v>
       </c>
       <c r="AM2">
-        <v>2.75</v>
+        <v>0.212</v>
       </c>
       <c r="AN2">
-        <v>-0.990990990990991</v>
+        <v>-0.9029126213592233</v>
       </c>
       <c r="AO2">
-        <v>-4.836363636363637</v>
+        <v>-40.91710758377425</v>
       </c>
       <c r="AP2">
-        <v>2.612612612612613</v>
+        <v>0.8446601941747571</v>
       </c>
       <c r="AQ2">
-        <v>-4.836363636363637</v>
+        <v>-109.433962264151</v>
       </c>
     </row>
     <row r="3">
@@ -713,22 +713,22 @@
         </is>
       </c>
       <c r="G3">
-        <v>-9.411057692307693</v>
+        <v>-4.482935153583617</v>
       </c>
       <c r="H3">
-        <v>-9.579326923076923</v>
+        <v>-4.573378839590443</v>
       </c>
       <c r="I3">
-        <v>-15.98557692307693</v>
+        <v>-7.918088737201365</v>
       </c>
       <c r="J3">
-        <v>-15.98557692307693</v>
+        <v>-7.918088737201365</v>
       </c>
       <c r="K3">
-        <v>-14.7</v>
+        <v>-23</v>
       </c>
       <c r="L3">
-        <v>-17.66826923076923</v>
+        <v>-7.849829351535836</v>
       </c>
       <c r="M3">
         <v>-0</v>
@@ -752,73 +752,73 @@
         <v>0</v>
       </c>
       <c r="U3">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="V3">
-        <v>0.1403508771929824</v>
+        <v>0.5333333333333333</v>
       </c>
       <c r="W3">
-        <v>-0.1620727673649393</v>
+        <v>-0.3662420382165605</v>
       </c>
       <c r="X3">
-        <v>0.1214544444345108</v>
+        <v>0.09937984110353799</v>
       </c>
       <c r="Y3">
-        <v>-0.2835272117994502</v>
+        <v>-0.4656218793200985</v>
       </c>
       <c r="Z3">
-        <v>0.07648464791321934</v>
+        <v>0.08668639053254439</v>
       </c>
       <c r="AA3">
-        <v>-1.222651222651223</v>
+        <v>-0.6863905325443788</v>
       </c>
       <c r="AB3">
-        <v>0.1186453400805256</v>
+        <v>0.08648018135294791</v>
       </c>
       <c r="AC3">
-        <v>-1.341296562731748</v>
+        <v>-0.7728707138973266</v>
       </c>
       <c r="AD3">
-        <v>11</v>
+        <v>18.6</v>
       </c>
       <c r="AE3">
         <v>0</v>
       </c>
       <c r="AF3">
-        <v>11</v>
+        <v>18.6</v>
       </c>
       <c r="AG3">
-        <v>-29</v>
+        <v>-17.4</v>
       </c>
       <c r="AH3">
-        <v>0.03716216216216216</v>
+        <v>0.21602787456446</v>
       </c>
       <c r="AI3">
-        <v>0.1453104359313078</v>
+        <v>0.1790182868142445</v>
       </c>
       <c r="AJ3">
-        <v>-0.11328125</v>
+        <v>-0.3473053892215568</v>
       </c>
       <c r="AK3">
-        <v>-0.8123249299719887</v>
+        <v>-0.2562592047128129</v>
       </c>
       <c r="AL3">
-        <v>2.75</v>
+        <v>0.5669999999999999</v>
       </c>
       <c r="AM3">
-        <v>2.75</v>
+        <v>0.212</v>
       </c>
       <c r="AN3">
-        <v>-0.990990990990991</v>
+        <v>-0.9029126213592233</v>
       </c>
       <c r="AO3">
-        <v>-4.836363636363637</v>
+        <v>-40.91710758377425</v>
       </c>
       <c r="AP3">
-        <v>2.612612612612613</v>
+        <v>0.8446601941747571</v>
       </c>
       <c r="AQ3">
-        <v>-4.836363636363637</v>
+        <v>-109.433962264151</v>
       </c>
     </row>
   </sheetData>
